--- a/catalog.clean.xlsx
+++ b/catalog.clean.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N823"/>
+  <dimension ref="A1:N836"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -36611,9 +36611,581 @@
         <v>plain</v>
       </c>
     </row>
+    <row r="824">
+      <c r="A824" t="str">
+        <v/>
+      </c>
+      <c r="B824" t="str">
+        <v>Clive Water Closet</v>
+      </c>
+      <c r="C824" t="str">
+        <v>ST-7014</v>
+      </c>
+      <c r="D824" t="str">
+        <v>Single Piece Wc</v>
+      </c>
+      <c r="E824" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F824">
+        <v>12500</v>
+      </c>
+      <c r="G824" t="str">
+        <v/>
+      </c>
+      <c r="H824" t="str">
+        <v/>
+      </c>
+      <c r="I824" t="str">
+        <v/>
+      </c>
+      <c r="J824" t="str">
+        <v>Clive wc</v>
+      </c>
+      <c r="K824" t="str">
+        <v/>
+      </c>
+      <c r="L824" t="str">
+        <v/>
+      </c>
+      <c r="M824" t="str">
+        <v/>
+      </c>
+      <c r="N824" t="str">
+        <v>plain</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="str">
+        <v/>
+      </c>
+      <c r="B825" t="str">
+        <v>Cinova Water Closet</v>
+      </c>
+      <c r="C825" t="str">
+        <v>ST-7036</v>
+      </c>
+      <c r="D825" t="str">
+        <v>Single Piece Wc</v>
+      </c>
+      <c r="E825" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F825">
+        <v>12750</v>
+      </c>
+      <c r="G825" t="str">
+        <v/>
+      </c>
+      <c r="H825" t="str">
+        <v/>
+      </c>
+      <c r="I825" t="str">
+        <v/>
+      </c>
+      <c r="J825" t="str">
+        <v>Cinova Wc</v>
+      </c>
+      <c r="K825" t="str">
+        <v/>
+      </c>
+      <c r="L825" t="str">
+        <v/>
+      </c>
+      <c r="M825" t="str">
+        <v/>
+      </c>
+      <c r="N825" t="str">
+        <v>plain</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="str">
+        <v/>
+      </c>
+      <c r="B826" t="str">
+        <v>Force Water Closet</v>
+      </c>
+      <c r="C826" t="str">
+        <v>ST-7027</v>
+      </c>
+      <c r="D826" t="str">
+        <v>Single Piece Wc</v>
+      </c>
+      <c r="E826" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F826">
+        <v>13793</v>
+      </c>
+      <c r="G826" t="str">
+        <v/>
+      </c>
+      <c r="H826" t="str">
+        <v/>
+      </c>
+      <c r="I826" t="str">
+        <v/>
+      </c>
+      <c r="J826" t="str">
+        <v>Force wc</v>
+      </c>
+      <c r="K826" t="str">
+        <v/>
+      </c>
+      <c r="L826" t="str">
+        <v/>
+      </c>
+      <c r="M826" t="str">
+        <v/>
+      </c>
+      <c r="N826" t="str">
+        <v>plain</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="str">
+        <v/>
+      </c>
+      <c r="B827" t="str">
+        <v>Glory Water Closet</v>
+      </c>
+      <c r="C827" t="str">
+        <v>ST-7030</v>
+      </c>
+      <c r="D827" t="str">
+        <v>Single Piece Wc</v>
+      </c>
+      <c r="E827" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F827">
+        <v>13933</v>
+      </c>
+      <c r="G827" t="str">
+        <v/>
+      </c>
+      <c r="H827" t="str">
+        <v/>
+      </c>
+      <c r="I827" t="str">
+        <v/>
+      </c>
+      <c r="J827" t="str">
+        <v>Glory wc</v>
+      </c>
+      <c r="K827" t="str">
+        <v/>
+      </c>
+      <c r="L827" t="str">
+        <v/>
+      </c>
+      <c r="M827" t="str">
+        <v/>
+      </c>
+      <c r="N827" t="str">
+        <v>plain</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="str">
+        <v/>
+      </c>
+      <c r="B828" t="str">
+        <v>Modenna Water Closet</v>
+      </c>
+      <c r="C828" t="str">
+        <v>ST-7031</v>
+      </c>
+      <c r="D828" t="str">
+        <v>Single Piece Wc</v>
+      </c>
+      <c r="E828" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F828">
+        <v>14488</v>
+      </c>
+      <c r="G828" t="str">
+        <v/>
+      </c>
+      <c r="H828" t="str">
+        <v/>
+      </c>
+      <c r="I828" t="str">
+        <v/>
+      </c>
+      <c r="J828" t="str">
+        <v>Modenna Wc</v>
+      </c>
+      <c r="K828" t="str">
+        <v/>
+      </c>
+      <c r="L828" t="str">
+        <v/>
+      </c>
+      <c r="M828" t="str">
+        <v/>
+      </c>
+      <c r="N828" t="str">
+        <v>plain</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="str">
+        <v/>
+      </c>
+      <c r="B829" t="str">
+        <v>Novella Water Closet</v>
+      </c>
+      <c r="C829" t="str">
+        <v>ST-7035</v>
+      </c>
+      <c r="D829" t="str">
+        <v>Single Piece Wc</v>
+      </c>
+      <c r="E829" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F829">
+        <v>14488</v>
+      </c>
+      <c r="G829" t="str">
+        <v/>
+      </c>
+      <c r="H829" t="str">
+        <v/>
+      </c>
+      <c r="I829" t="str">
+        <v/>
+      </c>
+      <c r="J829" t="str">
+        <v>Novella Wc</v>
+      </c>
+      <c r="K829" t="str">
+        <v/>
+      </c>
+      <c r="L829" t="str">
+        <v/>
+      </c>
+      <c r="M829" t="str">
+        <v/>
+      </c>
+      <c r="N829" t="str">
+        <v>plain</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="str">
+        <v/>
+      </c>
+      <c r="B830" t="str">
+        <v>Bravet Water Closet</v>
+      </c>
+      <c r="C830" t="str">
+        <v>ST-7032</v>
+      </c>
+      <c r="D830" t="str">
+        <v>Single Piece Wc</v>
+      </c>
+      <c r="E830" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F830">
+        <v>13933</v>
+      </c>
+      <c r="G830" t="str">
+        <v/>
+      </c>
+      <c r="H830" t="str">
+        <v/>
+      </c>
+      <c r="I830" t="str">
+        <v/>
+      </c>
+      <c r="J830" t="str">
+        <v>BRAVET Wc</v>
+      </c>
+      <c r="K830" t="str">
+        <v/>
+      </c>
+      <c r="L830" t="str">
+        <v/>
+      </c>
+      <c r="M830" t="str">
+        <v/>
+      </c>
+      <c r="N830" t="str">
+        <v>plain</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="str">
+        <v/>
+      </c>
+      <c r="B831" t="str">
+        <v>Wall Hung Rimless Modenna</v>
+      </c>
+      <c r="C831" t="str">
+        <v>ST-4024</v>
+      </c>
+      <c r="D831" t="str">
+        <v>Wall Hung Wc</v>
+      </c>
+      <c r="E831" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F831">
+        <v>13613</v>
+      </c>
+      <c r="G831" t="str">
+        <v/>
+      </c>
+      <c r="H831" t="str">
+        <v/>
+      </c>
+      <c r="I831" t="str">
+        <v/>
+      </c>
+      <c r="J831" t="str">
+        <v>MODENNA WALL HUNG</v>
+      </c>
+      <c r="K831" t="str">
+        <v/>
+      </c>
+      <c r="L831" t="str">
+        <v/>
+      </c>
+      <c r="M831" t="str">
+        <v/>
+      </c>
+      <c r="N831" t="str">
+        <v>plain</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="str">
+        <v/>
+      </c>
+      <c r="B832" t="str">
+        <v>Wall Hung Rimless Novella</v>
+      </c>
+      <c r="C832" t="str">
+        <v>ST-4023</v>
+      </c>
+      <c r="D832" t="str">
+        <v>Wall Hung Wc</v>
+      </c>
+      <c r="E832" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F832">
+        <v>13095</v>
+      </c>
+      <c r="G832" t="str">
+        <v/>
+      </c>
+      <c r="H832" t="str">
+        <v/>
+      </c>
+      <c r="I832" t="str">
+        <v/>
+      </c>
+      <c r="J832" t="str">
+        <v>NOVELLA WALL HUNG</v>
+      </c>
+      <c r="K832" t="str">
+        <v/>
+      </c>
+      <c r="L832" t="str">
+        <v/>
+      </c>
+      <c r="M832" t="str">
+        <v/>
+      </c>
+      <c r="N832" t="str">
+        <v>plain</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="str">
+        <v/>
+      </c>
+      <c r="B833" t="str">
+        <v>Wash Basin with Pedestal Neo</v>
+      </c>
+      <c r="C833" t="str">
+        <v>ST-1014</v>
+      </c>
+      <c r="D833" t="str">
+        <v>Basin With Pedestal</v>
+      </c>
+      <c r="E833" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F833">
+        <v>3646</v>
+      </c>
+      <c r="G833" t="str">
+        <v/>
+      </c>
+      <c r="H833" t="str">
+        <v/>
+      </c>
+      <c r="I833" t="str">
+        <v/>
+      </c>
+      <c r="J833" t="str">
+        <v>Neo Wb</v>
+      </c>
+      <c r="K833" t="str">
+        <v/>
+      </c>
+      <c r="L833" t="str">
+        <v/>
+      </c>
+      <c r="M833" t="str">
+        <v/>
+      </c>
+      <c r="N833" t="str">
+        <v>plain</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="str">
+        <v/>
+      </c>
+      <c r="B834" t="str">
+        <v>Wash Basin with Pedestal Cocoon</v>
+      </c>
+      <c r="C834" t="str">
+        <v>ST-1015</v>
+      </c>
+      <c r="D834" t="str">
+        <v>Basin With Pedestal</v>
+      </c>
+      <c r="E834" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F834">
+        <v>3308</v>
+      </c>
+      <c r="G834" t="str">
+        <v/>
+      </c>
+      <c r="H834" t="str">
+        <v/>
+      </c>
+      <c r="I834" t="str">
+        <v/>
+      </c>
+      <c r="J834" t="str">
+        <v>Cocoon Wb</v>
+      </c>
+      <c r="K834" t="str">
+        <v/>
+      </c>
+      <c r="L834" t="str">
+        <v/>
+      </c>
+      <c r="M834" t="str">
+        <v/>
+      </c>
+      <c r="N834" t="str">
+        <v>plain</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="str">
+        <v/>
+      </c>
+      <c r="B835" t="str">
+        <v>Wash Basin with Pedestal Cargo</v>
+      </c>
+      <c r="C835" t="str">
+        <v>ST-3012</v>
+      </c>
+      <c r="D835" t="str">
+        <v>Basin With Pedestal</v>
+      </c>
+      <c r="E835" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F835">
+        <v>3050</v>
+      </c>
+      <c r="G835" t="str">
+        <v/>
+      </c>
+      <c r="H835" t="str">
+        <v/>
+      </c>
+      <c r="I835" t="str">
+        <v/>
+      </c>
+      <c r="J835" t="str">
+        <v>CARGO WB</v>
+      </c>
+      <c r="K835" t="str">
+        <v/>
+      </c>
+      <c r="L835" t="str">
+        <v/>
+      </c>
+      <c r="M835" t="str">
+        <v/>
+      </c>
+      <c r="N835" t="str">
+        <v>plain</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="str">
+        <v/>
+      </c>
+      <c r="B836" t="str">
+        <v>Wash Basin with Pedestal Belleza</v>
+      </c>
+      <c r="C836" t="str">
+        <v>ST-1007</v>
+      </c>
+      <c r="D836" t="str">
+        <v>Basin With Pedestal</v>
+      </c>
+      <c r="E836" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F836">
+        <v>3866</v>
+      </c>
+      <c r="G836" t="str">
+        <v/>
+      </c>
+      <c r="H836" t="str">
+        <v/>
+      </c>
+      <c r="I836" t="str">
+        <v/>
+      </c>
+      <c r="J836" t="str">
+        <v>BELEZZA WB</v>
+      </c>
+      <c r="K836" t="str">
+        <v/>
+      </c>
+      <c r="L836" t="str">
+        <v/>
+      </c>
+      <c r="M836" t="str">
+        <v/>
+      </c>
+      <c r="N836" t="str">
+        <v>plain</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N823"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N836"/>
   </ignoredErrors>
 </worksheet>
 </file>